--- a/1-data/TableS3.xlsx
+++ b/1-data/TableS3.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,23 +379,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f__Alcaligenaceae</t>
+          <t>Acidaminococcaceae</t>
         </is>
       </c>
       <c r="B2">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>0.9541919335307547</v>
+        <v>0.8907961439734353</v>
       </c>
       <c r="D2">
-        <v>2.213890461914766E-88</v>
+        <v>3.205918135393263E-22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f__Bacillaceae</t>
+          <t>Akkermansiaceae</t>
         </is>
       </c>
       <c r="B3">
@@ -405,397 +405,477 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f__Bacteroidaceae</t>
+          <t>Anaerovoracaceae</t>
         </is>
       </c>
       <c r="B4">
-        <v>1201</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>0.9594416630479097</v>
+        <v>0.9657040557815593</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2.181800396773873E-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f__Bifidobacteriaceae</t>
+          <t>Bacillaceae</t>
         </is>
       </c>
       <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>0.2033062947937699</v>
-      </c>
-      <c r="D5">
-        <v>0.5998297512556078</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f__Clostridiaceae</t>
+          <t>Bacteroidaceae</t>
         </is>
       </c>
       <c r="B6">
-        <v>236</v>
+        <v>1066</v>
       </c>
       <c r="C6">
-        <v>0.9654455693911967</v>
+        <v>0.9644922062299845</v>
       </c>
       <c r="D6">
-        <v>1.180004141562231E-138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f__Coriobacteriaceae</t>
+          <t>Barnesiellaceae</t>
         </is>
       </c>
       <c r="B7">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="C7">
-        <v>0.9114052421198748</v>
+        <v>0.3391069612287379</v>
       </c>
       <c r="D7">
-        <v>5.665071250247359E-52</v>
+        <v>0.002388724674185241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f__Desulfovibrionaceae</t>
+          <t>Bifidobacteriaceae</t>
         </is>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>0.8043093959808779</v>
+        <v>0.3779104903825951</v>
       </c>
       <c r="D8">
-        <v>7.374736806967728E-07</v>
+        <v>0.4032530614181538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f__Enterobacteriaceae</t>
+          <t>Butyricicoccaceae</t>
         </is>
       </c>
       <c r="B9">
-        <v>4022</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>0.959311916234335</v>
+        <v>0.8363600623269597</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.0001929556147281175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f__Enterococcaceae</t>
+          <t>Clostridiaceae</t>
         </is>
       </c>
       <c r="B10">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C10">
-        <v>0.8353696204565505</v>
+        <v>0.9715778304752588</v>
       </c>
       <c r="D10">
-        <v>6.415893357616495E-61</v>
+        <v>1.226320731607719E-134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f__Erysipelotrichaceae</t>
+          <t>Coriobacteriaceae</t>
         </is>
       </c>
       <c r="B11">
-        <v>223</v>
+        <v>60</v>
       </c>
       <c r="C11">
-        <v>0.9455641992427937</v>
+        <v>0.9129146840754574</v>
       </c>
       <c r="D11">
-        <v>1.018864287957855E-109</v>
+        <v>3.048344502776484E-24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f__Eubacteriaceae</t>
+          <t>Desulfovibrionaceae</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>-0.930942731129252</v>
+        <v>0.897628387271637</v>
       </c>
       <c r="D12">
-        <v>0.2379750047237237</v>
+        <v>0.0004239562915684168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f__Lachnospiraceae</t>
+          <t>Eggerthellaceae</t>
         </is>
       </c>
       <c r="B13">
-        <v>1198</v>
+        <v>78</v>
       </c>
       <c r="C13">
-        <v>0.9287776657166942</v>
+        <v>0.8708485237584185</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>3.781371844134561E-25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f__Lactobacillaceae</t>
+          <t>Enterobacteriaceae</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>427</v>
+      </c>
+      <c r="C14">
+        <v>0.9768875138619086</v>
+      </c>
+      <c r="D14">
+        <v>6.47409519264347E-287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f__Peptococcaceae</t>
+          <t>Enterococcaceae</t>
         </is>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>210</v>
+      </c>
+      <c r="C15">
+        <v>0.8140103248042804</v>
+      </c>
+      <c r="D15">
+        <v>5.702734345852405E-51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f__Peptostreptococcaceae</t>
+          <t>Erysipelatoclostridiaceae</t>
         </is>
       </c>
       <c r="B16">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C16">
-        <v>0.9730854085883262</v>
+        <v>0.9716616978189182</v>
       </c>
       <c r="D16">
-        <v>8.069231247427778E-83</v>
+        <v>2.262947408612206E-98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f__Planococcaceae</t>
+          <t>Erysipelotrichaceae</t>
         </is>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>0.4789421381519232</v>
+      </c>
+      <c r="D17">
+        <v>0.115184660521813</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f__Porphyromonadaceae</t>
+          <t>Eubacteriaceae</t>
         </is>
       </c>
       <c r="B18">
-        <v>368</v>
-      </c>
-      <c r="C18">
-        <v>0.911154857477381</v>
-      </c>
-      <c r="D18">
-        <v>5.459846005111924E-143</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f__Prevotellaceae</t>
+          <t>Family XI</t>
         </is>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="C19">
-        <v>0.9300968195181253</v>
+        <v>0.9590777894875866</v>
       </c>
       <c r="D19">
-        <v>0.000809802519590829</v>
+        <v>2.955362685461476E-69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f__Rikenellaceae</t>
+          <t>Lachnospiraceae</t>
         </is>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>1050</v>
       </c>
       <c r="C20">
-        <v>-0.4973511477383292</v>
+        <v>0.8932530440770019</v>
       </c>
       <c r="D20">
-        <v>0.2560985002635067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f__Ruminococcaceae</t>
+          <t>Lactobacillaceae</t>
         </is>
       </c>
       <c r="B21">
-        <v>312</v>
-      </c>
-      <c r="C21">
-        <v>0.9446734577236381</v>
-      </c>
-      <c r="D21">
-        <v>4.040108717919057E-152</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f__Streptococcaceae</t>
+          <t>Marinifilaceae</t>
         </is>
       </c>
       <c r="B22">
-        <v>163</v>
-      </c>
-      <c r="C22">
-        <v>0.9797870366767661</v>
-      </c>
-      <c r="D22">
-        <v>1.939150158747291E-114</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f__Veillonellaceae</t>
+          <t>Morganellaceae</t>
         </is>
       </c>
       <c r="B23">
-        <v>486</v>
+        <v>163</v>
       </c>
       <c r="C23">
-        <v>0.9344832484241239</v>
+        <v>0.9936353319270215</v>
       </c>
       <c r="D23">
-        <v>3.123098622274734E-219</v>
+        <v>1.336659334932593E-154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f__Verrucomicrobiaceae</t>
+          <t>Oscillospiraceae</t>
         </is>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>202</v>
+      </c>
+      <c r="C24">
+        <v>0.9549657058904861</v>
+      </c>
+      <c r="D24">
+        <v>1.733554200305923E-107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f__[Barnesiellaceae]</t>
+          <t>Paenibacillaceae</t>
         </is>
       </c>
       <c r="B25">
-        <v>81</v>
-      </c>
-      <c r="C25">
-        <v>0.3088885103105353</v>
-      </c>
-      <c r="D25">
-        <v>0.005019971631687562</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f__[Mogibacteriaceae]</t>
+          <t>Peptostreptococcaceae</t>
         </is>
       </c>
       <c r="B26">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="C26">
-        <v>0.9675456044517169</v>
+        <v>0.9742239587657057</v>
       </c>
       <c r="D26">
-        <v>1.163396821897731E-17</v>
+        <v>3.250992738828064E-76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f__[Odoribacteraceae]</t>
+          <t>Porphyromonadaceae</t>
         </is>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="C27">
-        <v>-0.5910041246597486</v>
+        <v>0.9748525509600571</v>
       </c>
       <c r="D27">
-        <v>0.07197791682416642</v>
+        <v>5.633600653215502E-69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f__[Paraprevotellaceae]</t>
+          <t>Prevotellaceae</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>0.5307157958378564</v>
+      </c>
+      <c r="D28">
+        <v>0.0930243516979079</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f__[Tissierellaceae]</t>
+          <t>Rikenellaceae</t>
         </is>
       </c>
       <c r="B29">
-        <v>141</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>0.947206576532329</v>
+        <v>-0.6164219792610319</v>
       </c>
       <c r="D29">
-        <v>1.535636532779711E-70</v>
+        <v>0.1924798275231763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>o: Clostridiales</t>
+          <t>Ruminococcaceae</t>
         </is>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>0.892510079050044</v>
+      </c>
+      <c r="D30">
+        <v>1.338591464883495E-12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Selenomonadaceae</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Streptococcaceae</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>134</v>
+      </c>
+      <c r="C32">
+        <v>0.9844780177179346</v>
+      </c>
+      <c r="D32">
+        <v>1.243629505279122E-101</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sutterellaceae</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>148</v>
+      </c>
+      <c r="C33">
+        <v>0.9497232070016747</v>
+      </c>
+      <c r="D33">
+        <v>1.617942878503914E-75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tannerellaceae</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>241</v>
+      </c>
+      <c r="C34">
+        <v>0.8175027510710291</v>
+      </c>
+      <c r="D34">
+        <v>3.359772858473185E-59</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Veillonellaceae</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>403</v>
+      </c>
+      <c r="C35">
+        <v>0.9466884971671874</v>
+      </c>
+      <c r="D35">
+        <v>2.26621759279514E-199</v>
       </c>
     </row>
   </sheetData>
